--- a/my_dir/doc_preview_samples/sample.xlsx
+++ b/my_dir/doc_preview_samples/sample.xlsx
@@ -7,17 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="区域汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="季度仪表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'销售明细'!$A$3:$K$33</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;Q&quot;0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +34,63 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001E2761"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001E2761"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2761"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,16 +98,124 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -122,6 +286,218 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>分季度销售额</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'季度仪表'!B10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'季度仪表'!$A$11:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'季度仪表'!$B$11:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>元</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>产品线构成</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'季度仪表'!B17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'季度仪表'!$A$18:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'季度仪表'!$B$18:$B$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,55 +786,2100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>金额</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026 年度经营分析 · 参数表（黄色为可改区）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>123.45</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>大区</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>提成比例</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>大区</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>年度目标（元）</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>200</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>450000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>300</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>说明：提成比例与年度目标为手工填写区（黄色），改动后各表自动重算。</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E2761"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026 年销售明细（黄色为填写区，金额 / 提成 / 季度均为公式，请勿手工改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>大区</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>单价（元）</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>金额（元）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>提成比例</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>提成（元）</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-001</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>46026</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>郑十一</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H4" s="10">
+        <f>ROUND(F4*G4,2)</f>
+        <v/>
+      </c>
+      <c r="I4" s="11">
+        <f>VLOOKUP(C4,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J4" s="10">
+        <f>ROUND(H4*I4,2)</f>
+        <v/>
+      </c>
+      <c r="K4" s="12">
+        <f>CHOOSE(MONTH(B4),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-002</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>46031</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H5" s="14">
+        <f>ROUND(F5*G5,2)</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>VLOOKUP(C5,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f>ROUND(H5*I5,2)</f>
+        <v/>
+      </c>
+      <c r="K5" s="16">
+        <f>CHOOSE(MONTH(B5),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-003</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>46042</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H6" s="10">
+        <f>ROUND(F6*G6,2)</f>
+        <v/>
+      </c>
+      <c r="I6" s="11">
+        <f>VLOOKUP(C6,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J6" s="10">
+        <f>ROUND(H6*I6,2)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>CHOOSE(MONTH(B6),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-004</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H7" s="14">
+        <f>ROUND(F7*G7,2)</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>VLOOKUP(C7,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>ROUND(H7*I7,2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
+        <f>CHOOSE(MONTH(B7),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-005</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H8" s="10">
+        <f>ROUND(F8*G8,2)</f>
+        <v/>
+      </c>
+      <c r="I8" s="11">
+        <f>VLOOKUP(C8,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J8" s="10">
+        <f>ROUND(H8*I8,2)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>CHOOSE(MONTH(B8),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-006</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H9" s="14">
+        <f>ROUND(F9*G9,2)</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>VLOOKUP(C9,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>ROUND(H9*I9,2)</f>
+        <v/>
+      </c>
+      <c r="K9" s="16">
+        <f>CHOOSE(MONTH(B9),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-007</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H10" s="10">
+        <f>ROUND(F10*G10,2)</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>VLOOKUP(C10,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J10" s="10">
+        <f>ROUND(H10*I10,2)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>CHOOSE(MONTH(B10),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-008</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H11" s="14">
+        <f>ROUND(F11*G11,2)</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>VLOOKUP(C11,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>ROUND(H11*I11,2)</f>
+        <v/>
+      </c>
+      <c r="K11" s="16">
+        <f>CHOOSE(MONTH(B11),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-009</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>46129</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H12" s="10">
+        <f>ROUND(F12*G12,2)</f>
+        <v/>
+      </c>
+      <c r="I12" s="11">
+        <f>VLOOKUP(C12,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J12" s="10">
+        <f>ROUND(H12*I12,2)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>CHOOSE(MONTH(B12),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-010</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H13" s="14">
+        <f>ROUND(F13*G13,2)</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>VLOOKUP(C13,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>ROUND(H13*I13,2)</f>
+        <v/>
+      </c>
+      <c r="K13" s="16">
+        <f>CHOOSE(MONTH(B13),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-011</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H14" s="10">
+        <f>ROUND(F14*G14,2)</f>
+        <v/>
+      </c>
+      <c r="I14" s="11">
+        <f>VLOOKUP(C14,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J14" s="10">
+        <f>ROUND(H14*I14,2)</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>CHOOSE(MONTH(B14),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-012</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H15" s="14">
+        <f>ROUND(F15*G15,2)</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>VLOOKUP(C15,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>ROUND(H15*I15,2)</f>
+        <v/>
+      </c>
+      <c r="K15" s="16">
+        <f>CHOOSE(MONTH(B15),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-013</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H16" s="10">
+        <f>ROUND(F16*G16,2)</f>
+        <v/>
+      </c>
+      <c r="I16" s="11">
+        <f>VLOOKUP(C16,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J16" s="10">
+        <f>ROUND(H16*I16,2)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>CHOOSE(MONTH(B16),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-014</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H17" s="14">
+        <f>ROUND(F17*G17,2)</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>VLOOKUP(C17,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>ROUND(H17*I17,2)</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
+        <f>CHOOSE(MONTH(B17),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-015</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H18" s="10">
+        <f>ROUND(F18*G18,2)</f>
+        <v/>
+      </c>
+      <c r="I18" s="11">
+        <f>VLOOKUP(C18,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J18" s="10">
+        <f>ROUND(H18*I18,2)</f>
+        <v/>
+      </c>
+      <c r="K18" s="12">
+        <f>CHOOSE(MONTH(B18),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-016</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H19" s="14">
+        <f>ROUND(F19*G19,2)</f>
+        <v/>
+      </c>
+      <c r="I19" s="15">
+        <f>VLOOKUP(C19,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>ROUND(H19*I19,2)</f>
+        <v/>
+      </c>
+      <c r="K19" s="16">
+        <f>CHOOSE(MONTH(B19),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-017</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H20" s="10">
+        <f>ROUND(F20*G20,2)</f>
+        <v/>
+      </c>
+      <c r="I20" s="11">
+        <f>VLOOKUP(C20,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J20" s="10">
+        <f>ROUND(H20*I20,2)</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>CHOOSE(MONTH(B20),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-018</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H21" s="14">
+        <f>ROUND(F21*G21,2)</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>VLOOKUP(C21,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>ROUND(H21*I21,2)</f>
+        <v/>
+      </c>
+      <c r="K21" s="16">
+        <f>CHOOSE(MONTH(B21),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-019</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H22" s="10">
+        <f>ROUND(F22*G22,2)</f>
+        <v/>
+      </c>
+      <c r="I22" s="11">
+        <f>VLOOKUP(C22,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10">
+        <f>ROUND(H22*I22,2)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>CHOOSE(MONTH(B22),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-020</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>郑十一</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H23" s="14">
+        <f>ROUND(F23*G23,2)</f>
+        <v/>
+      </c>
+      <c r="I23" s="15">
+        <f>VLOOKUP(C23,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>ROUND(H23*I23,2)</f>
+        <v/>
+      </c>
+      <c r="K23" s="16">
+        <f>CHOOSE(MONTH(B23),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-021</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H24" s="10">
+        <f>ROUND(F24*G24,2)</f>
+        <v/>
+      </c>
+      <c r="I24" s="11">
+        <f>VLOOKUP(C24,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J24" s="10">
+        <f>ROUND(H24*I24,2)</f>
+        <v/>
+      </c>
+      <c r="K24" s="12">
+        <f>CHOOSE(MONTH(B24),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-022</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H25" s="14">
+        <f>ROUND(F25*G25,2)</f>
+        <v/>
+      </c>
+      <c r="I25" s="15">
+        <f>VLOOKUP(C25,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>ROUND(H25*I25,2)</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
+        <f>CHOOSE(MONTH(B25),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-023</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H26" s="10">
+        <f>ROUND(F26*G26,2)</f>
+        <v/>
+      </c>
+      <c r="I26" s="11">
+        <f>VLOOKUP(C26,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J26" s="10">
+        <f>ROUND(H26*I26,2)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>CHOOSE(MONTH(B26),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-024</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H27" s="14">
+        <f>ROUND(F27*G27,2)</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>VLOOKUP(C27,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>ROUND(H27*I27,2)</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
+        <f>CHOOSE(MONTH(B27),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-025</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>郑十一</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H28" s="10">
+        <f>ROUND(F28*G28,2)</f>
+        <v/>
+      </c>
+      <c r="I28" s="11">
+        <f>VLOOKUP(C28,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J28" s="10">
+        <f>ROUND(H28*I28,2)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>CHOOSE(MONTH(B28),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-026</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>46337</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H29" s="14">
+        <f>ROUND(F29*G29,2)</f>
+        <v/>
+      </c>
+      <c r="I29" s="15">
+        <f>VLOOKUP(C29,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>ROUND(H29*I29,2)</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>CHOOSE(MONTH(B29),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-027</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>46346</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H30" s="10">
+        <f>ROUND(F30*G30,2)</f>
+        <v/>
+      </c>
+      <c r="I30" s="11">
+        <f>VLOOKUP(C30,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J30" s="10">
+        <f>ROUND(H30*I30,2)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>CHOOSE(MONTH(B30),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-028</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H31" s="14">
+        <f>ROUND(F31*G31,2)</f>
+        <v/>
+      </c>
+      <c r="I31" s="15">
+        <f>VLOOKUP(C31,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>ROUND(H31*I31,2)</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>CHOOSE(MONTH(B31),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>DD2026-029</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>46365</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>吴十</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H32" s="10">
+        <f>ROUND(F32*G32,2)</f>
+        <v/>
+      </c>
+      <c r="I32" s="11">
+        <f>VLOOKUP(C32,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J32" s="10">
+        <f>ROUND(H32*I32,2)</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>CHOOSE(MONTH(B32),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>DD2026-030</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>46374</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>郑十一</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H33" s="14">
+        <f>ROUND(F33*G33,2)</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>VLOOKUP(C33,参数表!$A$3:$B$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="J33" s="14">
+        <f>ROUND(H33*I33,2)</f>
+        <v/>
+      </c>
+      <c r="K33" s="16">
+        <f>CHOOSE(MONTH(B33),1,1,1,2,2,2,3,3,3,4,4,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="19">
+        <f>SUM(F4:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="20">
+        <f>SUM(H4:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="20">
+        <f>SUM(J4:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K33"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H4:H33">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="200000"/>
+        <color rgb="001E2761"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C4:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="请从下拉选择大区" type="list">
+      <formula1>"华东,华南,华北"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C2026 年销售明细（内部资料）</oddHeader>
+    <oddFooter>&amp;C第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026 年大区汇总（全部为公式，自动随明细与参数变化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>大区</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>订单数</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>销售额（元）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>提成（元）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>年度目标（元）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>达成率</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>平均单（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>COUNTIFS(销售明细!$C$4:$C$33,A4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="10">
+        <f>SUMIFS(销售明细!$H$4:$H$33,销售明细!$C$4:$C$33,A4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="10">
+        <f>SUMIFS(销售明细!$J$4:$J$33,销售明细!$C$4:$C$33,A4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="21">
+        <f>VLOOKUP(A4,参数表!$D$3:$E$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="F4" s="22">
+        <f>IFERROR(C4/E4,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="10">
+        <f>IFERROR(C4/B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B5" s="23">
+        <f>COUNTIFS(销售明细!$C$4:$C$33,A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="14">
+        <f>SUMIFS(销售明细!$H$4:$H$33,销售明细!$C$4:$C$33,A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="14">
+        <f>SUMIFS(销售明细!$J$4:$J$33,销售明细!$C$4:$C$33,A5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="23">
+        <f>VLOOKUP(A5,参数表!$D$3:$E$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
+        <f>IFERROR(C5/E5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>IFERROR(C5/B5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B6" s="21">
+        <f>COUNTIFS(销售明细!$C$4:$C$33,A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="10">
+        <f>SUMIFS(销售明细!$H$4:$H$33,销售明细!$C$4:$C$33,A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>SUMIFS(销售明细!$J$4:$J$33,销售明细!$C$4:$C$33,A6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>VLOOKUP(A6,参数表!$D$3:$E$5,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>IFERROR(C6/E6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>IFERROR(C6/B6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>SUM(B4:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27">
+        <f>SUM(C4:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>SUM(D4:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>SUM(E4:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>IFERROR(C7/E7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="25" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F4:F7">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0027AE60"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026 年经营仪表盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>核心指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>总销售额（元）</t>
+        </is>
+      </c>
+      <c r="B3" s="27">
+        <f>SUM(销售明细!H4:H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>总提成（元）</t>
+        </is>
+      </c>
+      <c r="B4" s="27">
+        <f>SUM(销售明细!J4:J33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>订单总数</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>COUNTA(销售明细!A4:A33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>最大单（元）</t>
+        </is>
+      </c>
+      <c r="B6" s="27">
+        <f>MAX(销售明细!H4:H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>平均单（元）</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
+        <f>AVERAGE(销售明细!H4:H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>年度总达成率</t>
+        </is>
+      </c>
+      <c r="B8" s="28">
+        <f>IFERROR(B3/区域汇总!E7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>分季度销售额</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>销售额（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>SUMIF(销售明细!$K$4:$K$33,1,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>SUMIF(销售明细!$K$4:$K$33,2,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>SUMIF(销售明细!$K$4:$K$33,3,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <f>SUMIF(销售明细!$K$4:$K$33,4,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>产品线构成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>销售额（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>标准版</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>SUMIF(销售明细!$E$4:$E$33,A18,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>专业版</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <f>SUMIF(销售明细!$E$4:$E$33,A19,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>旗舰版</t>
+        </is>
+      </c>
+      <c r="B20" s="10">
+        <f>SUMIF(销售明细!$E$4:$E$33,A20,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>定制服务</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>SUMIF(销售明细!$E$4:$E$33,A21,销售明细!$H$4:$H$33)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>